--- a/output/pdf_financials_xlsx/SEC.xlsx
+++ b/output/pdf_financials_xlsx/SEC.xlsx
@@ -879,40 +879,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>6.158</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>3.285</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>4.184</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>6.972</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>15.991</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>20.059</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>9.208</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>28.232</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>64.129</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>58.942</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>53.027</v>
       </c>
     </row>
     <row r="13">
@@ -1602,40 +1602,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>268.248</v>
+        <v>262.09</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>162.453</v>
+        <v>159.663</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-105.678</v>
+        <v>-108.963</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>137.787</v>
+        <v>133.603</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>221.089</v>
+        <v>214.117</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-178.542</v>
+        <v>-194.533</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>128.61</v>
+        <v>108.551</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>836.822</v>
+        <v>827.614</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-367.832</v>
+        <v>-396.064</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>101.473</v>
+        <v>37.344</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>316.734</v>
+        <v>257.792</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>177.116</v>
+        <v>124.089</v>
       </c>
     </row>
     <row r="28">
@@ -1688,40 +1688,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>268.248</v>
+        <v>262.09</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>162.453</v>
+        <v>159.663</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-105.678</v>
+        <v>-108.963</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>137.787</v>
+        <v>133.603</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>221.089</v>
+        <v>214.117</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-178.542</v>
+        <v>-194.533</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>128.61</v>
+        <v>108.551</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>836.822</v>
+        <v>827.614</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-367.832</v>
+        <v>-396.064</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>101.473</v>
+        <v>37.344</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>316.734</v>
+        <v>257.792</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>177.116</v>
+        <v>124.089</v>
       </c>
     </row>
     <row r="30">
@@ -1731,40 +1731,40 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>1595.764425936942</v>
+        <v>1559.131469363474</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1338.714462299135</v>
+        <v>1315.723114956737</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-679.5575847212398</v>
+        <v>-700.6816281911132</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>885.8052073288333</v>
+        <v>858.9071038251366</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>844.1411171776565</v>
+        <v>817.5212859379176</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-637.7411058722676</v>
+        <v>-694.8599799971424</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>353.489266965341</v>
+        <v>298.3563752301899</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1871.833758332215</v>
+        <v>1851.236970429025</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-477.0409949810004</v>
+        <v>-513.6550507736004</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>70.43654512261996</v>
+        <v>25.92199246163137</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>240.161050620242</v>
+        <v>195.4687452609869</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>114.9290437287894</v>
+        <v>80.5202810997411</v>
       </c>
     </row>
     <row r="31">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">

--- a/output/pdf_financials_xlsx/SEC.xlsx
+++ b/output/pdf_financials_xlsx/SEC.xlsx
@@ -5726,34 +5726,34 @@
         <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-3.804</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-6.06</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-8.371</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-11.685</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-6.172</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-28.001</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-8.936999999999999</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-2.085</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-9.654999999999999</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-6.111</v>
       </c>
     </row>
     <row r="122">
@@ -10824,7 +10824,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -18274,7 +18278,11 @@
           <t>Share of profit (loss) of associates 7</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -18574,7 +18582,11 @@
           <t>Share of profit of associates 7</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -19384,7 +19396,11 @@
           <t>Share of profit (loss) of associates 7</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E192" s="5" t="n">
         <v>-9.909000000000001</v>
       </c>
